--- a/data/nzd0589/nzd0589.xlsx
+++ b/data/nzd0589/nzd0589.xlsx
@@ -15689,9 +15689,15 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0756</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -15739,9 +15745,15 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.0443</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.1473</v>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -15789,9 +15801,15 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0288</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0717</v>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -15839,9 +15857,15 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0487</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.141</v>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -15889,9 +15913,15 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0356</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0611</v>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -15939,9 +15969,15 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.0689</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -15989,9 +16025,15 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0624</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -16039,9 +16081,15 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0443</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.1106</v>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>

--- a/data/nzd0589/nzd0589.xlsx
+++ b/data/nzd0589/nzd0589.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J467"/>
+  <dimension ref="A1:J468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17248,6 +17248,42 @@
       <c r="J467" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:27:14+00:00</t>
+        </is>
+      </c>
+      <c r="B468" t="n">
+        <v>345.36</v>
+      </c>
+      <c r="C468" t="n">
+        <v>210.94</v>
+      </c>
+      <c r="D468" t="n">
+        <v>242.53</v>
+      </c>
+      <c r="E468" t="n">
+        <v>219.82</v>
+      </c>
+      <c r="F468" t="n">
+        <v>209.67</v>
+      </c>
+      <c r="G468" t="n">
+        <v>232.62</v>
+      </c>
+      <c r="H468" t="n">
+        <v>214.43</v>
+      </c>
+      <c r="I468" t="n">
+        <v>201.89</v>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -17262,7 +17298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B502"/>
+  <dimension ref="A1:B503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22285,6 +22321,16 @@
       </c>
       <c r="B502" t="n">
         <v>0.33</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>0.57</v>
       </c>
     </row>
   </sheetData>
@@ -22447,28 +22493,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09447868960728645</v>
+        <v>0.09824540626468763</v>
       </c>
       <c r="J2" t="n">
+        <v>467</v>
+      </c>
+      <c r="K2" t="n">
         <v>466</v>
       </c>
-      <c r="K2" t="n">
-        <v>465</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0009271454270259882</v>
+        <v>0.001006731430387542</v>
       </c>
       <c r="M2" t="n">
-        <v>15.85919991457064</v>
+        <v>15.83614362134256</v>
       </c>
       <c r="N2" t="n">
-        <v>534.9963833412679</v>
+        <v>534.0210808586653</v>
       </c>
       <c r="O2" t="n">
-        <v>23.12998883141252</v>
+        <v>23.10889614106795</v>
       </c>
       <c r="P2" t="n">
-        <v>333.8594590504483</v>
+        <v>333.8202387173151</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22519,28 +22565,28 @@
         <v>0.1473</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09014449067958637</v>
+        <v>0.08875192770993187</v>
       </c>
       <c r="J3" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K3" t="n">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03851060844348786</v>
+        <v>0.03746294982503384</v>
       </c>
       <c r="M3" t="n">
-        <v>2.641571917814297</v>
+        <v>2.641684293614307</v>
       </c>
       <c r="N3" t="n">
-        <v>11.29567106149709</v>
+        <v>11.29503923635317</v>
       </c>
       <c r="O3" t="n">
-        <v>3.360903310346356</v>
+        <v>3.360809312703291</v>
       </c>
       <c r="P3" t="n">
-        <v>211.8821648048377</v>
+        <v>211.8966661745733</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22591,28 +22637,28 @@
         <v>0.0717</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2525960308441159</v>
+        <v>0.2519203846844371</v>
       </c>
       <c r="J4" t="n">
+        <v>467</v>
+      </c>
+      <c r="K4" t="n">
         <v>466</v>
       </c>
-      <c r="K4" t="n">
-        <v>465</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.08893387990080193</v>
+        <v>0.08885924056236905</v>
       </c>
       <c r="M4" t="n">
-        <v>4.447817146621966</v>
+        <v>4.440963832790231</v>
       </c>
       <c r="N4" t="n">
-        <v>36.04372557446919</v>
+        <v>35.97186621964443</v>
       </c>
       <c r="O4" t="n">
-        <v>6.003642692105284</v>
+        <v>5.997655060075098</v>
       </c>
       <c r="P4" t="n">
-        <v>237.4665338059193</v>
+        <v>237.4736070772949</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22663,28 +22709,28 @@
         <v>0.141</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1482300125359998</v>
+        <v>0.1470490015440946</v>
       </c>
       <c r="J5" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K5" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08336336042876225</v>
+        <v>0.08239877309443555</v>
       </c>
       <c r="M5" t="n">
-        <v>2.905501592110596</v>
+        <v>2.904503555825709</v>
       </c>
       <c r="N5" t="n">
-        <v>13.41894991879566</v>
+        <v>13.40715836375815</v>
       </c>
       <c r="O5" t="n">
-        <v>3.663188490754423</v>
+        <v>3.661578670977608</v>
       </c>
       <c r="P5" t="n">
-        <v>218.7287130627226</v>
+        <v>218.7410126787389</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22735,28 +22781,28 @@
         <v>0.0611</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4261479110424566</v>
+        <v>-0.4256789591181829</v>
       </c>
       <c r="J6" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K6" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3634799588749945</v>
+        <v>0.3639936054690652</v>
       </c>
       <c r="M6" t="n">
-        <v>3.176224529939507</v>
+        <v>3.172153753568926</v>
       </c>
       <c r="N6" t="n">
-        <v>17.66349262378431</v>
+        <v>17.62834067058844</v>
       </c>
       <c r="O6" t="n">
-        <v>4.202795810384357</v>
+        <v>4.198611755162466</v>
       </c>
       <c r="P6" t="n">
-        <v>219.8061806485424</v>
+        <v>219.8012967578435</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22807,28 +22853,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0006546578898786307</v>
+        <v>0.002146958705412666</v>
       </c>
       <c r="J7" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K7" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L7" t="n">
-        <v>1.366255432011521e-06</v>
+        <v>1.4680996742511e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>3.174229234547003</v>
+        <v>3.182273315496089</v>
       </c>
       <c r="N7" t="n">
-        <v>17.42290462435319</v>
+        <v>17.48094084514688</v>
       </c>
       <c r="O7" t="n">
-        <v>4.17407530171093</v>
+        <v>4.181021507376742</v>
       </c>
       <c r="P7" t="n">
-        <v>225.9397689873294</v>
+        <v>225.910591605761</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22879,28 +22925,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00121739797004988</v>
+        <v>0.001436865221104704</v>
       </c>
       <c r="J8" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K8" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L8" t="n">
-        <v>3.335631116541116e-06</v>
+        <v>4.667884481945883e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>3.054179717475093</v>
+        <v>3.049243423802199</v>
       </c>
       <c r="N8" t="n">
-        <v>24.67799790124874</v>
+        <v>24.62573930513238</v>
       </c>
       <c r="O8" t="n">
-        <v>4.967695431610994</v>
+        <v>4.962432801069691</v>
       </c>
       <c r="P8" t="n">
-        <v>213.8772163302055</v>
+        <v>213.8749306927858</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22951,28 +22997,28 @@
         <v>0.1106</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1188760353481143</v>
+        <v>-0.1176522990164869</v>
       </c>
       <c r="J9" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K9" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04400776039692</v>
+        <v>0.04329017302266469</v>
       </c>
       <c r="M9" t="n">
-        <v>2.948890722095808</v>
+        <v>2.948815847728024</v>
       </c>
       <c r="N9" t="n">
-        <v>17.05053324838308</v>
+        <v>17.03221333545849</v>
       </c>
       <c r="O9" t="n">
-        <v>4.129229134884994</v>
+        <v>4.127010217513217</v>
       </c>
       <c r="P9" t="n">
-        <v>202.1037747783564</v>
+        <v>202.0910302001201</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23010,7 +23056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J467"/>
+  <dimension ref="A1:J468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47281,6 +47327,58 @@
         </is>
       </c>
     </row>
+    <row r="468">
+      <c r="A468" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:27:14+00:00</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>-46.897042699838586,168.13076649776178</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>-46.89783429825452,168.12907250689273</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>-46.898534278056395,168.12955016269711</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>-46.89895137495121,168.12990702600308</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>-46.899531609195506,168.13054009046596</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>-46.89990523227895,168.13148518264424</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>-46.90018457595863,168.13221358097843</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>-46.9004627246178,168.13319424896042</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0589/nzd0589.xlsx
+++ b/data/nzd0589/nzd0589.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J468"/>
+  <dimension ref="A1:J469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17282,6 +17282,42 @@
         <v>201.89</v>
       </c>
       <c r="J468" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-29 22:27:35+00:00</t>
+        </is>
+      </c>
+      <c r="B469" t="n">
+        <v>348.98</v>
+      </c>
+      <c r="C469" t="n">
+        <v>210.85</v>
+      </c>
+      <c r="D469" t="n">
+        <v>243</v>
+      </c>
+      <c r="E469" t="n">
+        <v>219.13</v>
+      </c>
+      <c r="F469" t="n">
+        <v>209.52</v>
+      </c>
+      <c r="G469" t="n">
+        <v>234.08</v>
+      </c>
+      <c r="H469" t="n">
+        <v>215.14</v>
+      </c>
+      <c r="I469" t="n">
+        <v>202.29</v>
+      </c>
+      <c r="J469" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -17298,7 +17334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B503"/>
+  <dimension ref="A1:B504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22331,6 +22367,16 @@
       </c>
       <c r="B503" t="n">
         <v>0.57</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2025-12-29 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>0.66</v>
       </c>
     </row>
   </sheetData>
@@ -22493,28 +22539,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09824540626468763</v>
+        <v>0.1034866596786767</v>
       </c>
       <c r="J2" t="n">
+        <v>468</v>
+      </c>
+      <c r="K2" t="n">
         <v>467</v>
       </c>
-      <c r="K2" t="n">
-        <v>466</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.001006731430387542</v>
+        <v>0.001121287887824174</v>
       </c>
       <c r="M2" t="n">
-        <v>15.83614362134256</v>
+        <v>15.81740209529287</v>
       </c>
       <c r="N2" t="n">
-        <v>534.0210808586653</v>
+        <v>533.213142170859</v>
       </c>
       <c r="O2" t="n">
-        <v>23.10889614106795</v>
+        <v>23.09140840596041</v>
       </c>
       <c r="P2" t="n">
-        <v>333.8202387173151</v>
+        <v>333.7655571174915</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22565,28 +22611,28 @@
         <v>0.1473</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08875192770993187</v>
+        <v>0.08733564670847145</v>
       </c>
       <c r="J3" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K3" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03746294982503384</v>
+        <v>0.03640346392653027</v>
       </c>
       <c r="M3" t="n">
-        <v>2.641684293614307</v>
+        <v>2.641899678001904</v>
       </c>
       <c r="N3" t="n">
-        <v>11.29503923635317</v>
+        <v>11.29535276611501</v>
       </c>
       <c r="O3" t="n">
-        <v>3.360809312703291</v>
+        <v>3.360855957358929</v>
       </c>
       <c r="P3" t="n">
-        <v>211.8966661745733</v>
+        <v>211.9114437763003</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22637,28 +22683,28 @@
         <v>0.0717</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2519203846844371</v>
+        <v>0.2514416243843697</v>
       </c>
       <c r="J4" t="n">
+        <v>468</v>
+      </c>
+      <c r="K4" t="n">
         <v>467</v>
       </c>
-      <c r="K4" t="n">
-        <v>466</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.08885924056236905</v>
+        <v>0.08891613776307317</v>
       </c>
       <c r="M4" t="n">
-        <v>4.440963832790231</v>
+        <v>4.433348870942426</v>
       </c>
       <c r="N4" t="n">
-        <v>35.97186621964443</v>
+        <v>35.89760308342955</v>
       </c>
       <c r="O4" t="n">
-        <v>5.997655060075098</v>
+        <v>5.991460847191572</v>
       </c>
       <c r="P4" t="n">
-        <v>237.4736070772949</v>
+        <v>237.4786289842496</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22709,28 +22755,28 @@
         <v>0.141</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1470490015440946</v>
+        <v>0.1455874876044856</v>
       </c>
       <c r="J5" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K5" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08239877309443555</v>
+        <v>0.08109628156795046</v>
       </c>
       <c r="M5" t="n">
-        <v>2.904503555825709</v>
+        <v>2.904731225220434</v>
       </c>
       <c r="N5" t="n">
-        <v>13.40715836375815</v>
+        <v>13.40454183711812</v>
       </c>
       <c r="O5" t="n">
-        <v>3.661578670977608</v>
+        <v>3.661221358661358</v>
       </c>
       <c r="P5" t="n">
-        <v>218.7410126787389</v>
+        <v>218.7562635779196</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22781,28 +22827,28 @@
         <v>0.0611</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4256789591181829</v>
+        <v>-0.4252707742062529</v>
       </c>
       <c r="J6" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K6" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3639936054690652</v>
+        <v>0.364580708942997</v>
       </c>
       <c r="M6" t="n">
-        <v>3.172153753568926</v>
+        <v>3.167738890477199</v>
       </c>
       <c r="N6" t="n">
-        <v>17.62834067058844</v>
+        <v>17.59270377581113</v>
       </c>
       <c r="O6" t="n">
-        <v>4.198611755162466</v>
+        <v>4.194365717937711</v>
       </c>
       <c r="P6" t="n">
-        <v>219.8012967578435</v>
+        <v>219.7970373479465</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22853,28 +22899,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002146958705412666</v>
+        <v>0.005531046808272305</v>
       </c>
       <c r="J7" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K7" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4680996742511e-05</v>
+        <v>9.709806339752713e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>3.182273315496089</v>
+        <v>3.193294617741275</v>
       </c>
       <c r="N7" t="n">
-        <v>17.48094084514688</v>
+        <v>17.5831520777385</v>
       </c>
       <c r="O7" t="n">
-        <v>4.181021507376742</v>
+        <v>4.193226928957995</v>
       </c>
       <c r="P7" t="n">
-        <v>225.910591605761</v>
+        <v>225.8752786435809</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22925,28 +22971,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001436865221104704</v>
+        <v>0.00195046553254177</v>
       </c>
       <c r="J8" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K8" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L8" t="n">
-        <v>4.667884481945883e-06</v>
+        <v>8.639537531496266e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>3.049243423802199</v>
+        <v>3.046460510686613</v>
       </c>
       <c r="N8" t="n">
-        <v>24.62573930513238</v>
+        <v>24.5763348978833</v>
       </c>
       <c r="O8" t="n">
-        <v>4.962432801069691</v>
+        <v>4.957452460476379</v>
       </c>
       <c r="P8" t="n">
-        <v>213.8749306927858</v>
+        <v>213.869571273107</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22997,28 +23043,28 @@
         <v>0.1106</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1176522990164869</v>
+        <v>-0.1162691588262145</v>
       </c>
       <c r="J9" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K9" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04329017302266469</v>
+        <v>0.04245095225522721</v>
       </c>
       <c r="M9" t="n">
-        <v>2.948815847728024</v>
+        <v>2.949526985334749</v>
       </c>
       <c r="N9" t="n">
-        <v>17.03221333545849</v>
+        <v>17.01913396789699</v>
       </c>
       <c r="O9" t="n">
-        <v>4.127010217513217</v>
+        <v>4.125425307516426</v>
       </c>
       <c r="P9" t="n">
-        <v>202.0910302001201</v>
+        <v>202.0765971310792</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23056,7 +23102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J468"/>
+  <dimension ref="A1:J469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47379,6 +47425,58 @@
         </is>
       </c>
     </row>
+    <row r="469">
+      <c r="A469" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-29 22:27:35+00:00</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>-46.897040699661325,168.13081385202682</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>-46.89783434796424,168.12907132955908</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>-46.898534019411514,168.12955631116253</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>-46.898955683727294,168.12990052451084</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>-46.899532545227515,168.13053867615355</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>-46.899896122932496,168.13149895065308</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>-46.90017837599549,168.13221576703472</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>-46.900459231668215,168.13319548048622</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0589/nzd0589.xlsx
+++ b/data/nzd0589/nzd0589.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J469"/>
+  <dimension ref="A1:J470"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17320,6 +17320,42 @@
       <c r="J469" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:27:30+00:00</t>
+        </is>
+      </c>
+      <c r="B470" t="n">
+        <v>347.01</v>
+      </c>
+      <c r="C470" t="n">
+        <v>211.07</v>
+      </c>
+      <c r="D470" t="n">
+        <v>239.83</v>
+      </c>
+      <c r="E470" t="n">
+        <v>214.78</v>
+      </c>
+      <c r="F470" t="n">
+        <v>205.68</v>
+      </c>
+      <c r="G470" t="n">
+        <v>235.15</v>
+      </c>
+      <c r="H470" t="n">
+        <v>213.84</v>
+      </c>
+      <c r="I470" t="n">
+        <v>201.2</v>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -17334,7 +17370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B504"/>
+  <dimension ref="A1:B505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22377,6 +22413,16 @@
       </c>
       <c r="B504" t="n">
         <v>0.66</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>-0.25</v>
       </c>
     </row>
   </sheetData>
@@ -22539,28 +22585,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1034866596786767</v>
+        <v>0.1078943882607164</v>
       </c>
       <c r="J2" t="n">
+        <v>469</v>
+      </c>
+      <c r="K2" t="n">
         <v>468</v>
       </c>
-      <c r="K2" t="n">
-        <v>467</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.001121287887824174</v>
+        <v>0.001223859797066296</v>
       </c>
       <c r="M2" t="n">
-        <v>15.81740209529287</v>
+        <v>15.79615583140257</v>
       </c>
       <c r="N2" t="n">
-        <v>533.213142170859</v>
+        <v>532.3072196735257</v>
       </c>
       <c r="O2" t="n">
-        <v>23.09140840596041</v>
+        <v>23.07178405918202</v>
       </c>
       <c r="P2" t="n">
-        <v>333.7655571174915</v>
+        <v>333.7192576250069</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22611,28 +22657,28 @@
         <v>0.1473</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08733564670847145</v>
+        <v>0.0860035828920071</v>
       </c>
       <c r="J3" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K3" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03640346392653027</v>
+        <v>0.03543444475561075</v>
       </c>
       <c r="M3" t="n">
-        <v>2.641899678001904</v>
+        <v>2.641721261881967</v>
       </c>
       <c r="N3" t="n">
-        <v>11.29535276611501</v>
+        <v>11.29252622826453</v>
       </c>
       <c r="O3" t="n">
-        <v>3.360855957358929</v>
+        <v>3.360435422421405</v>
       </c>
       <c r="P3" t="n">
-        <v>211.9114437763003</v>
+        <v>211.9254378388652</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22683,28 +22729,28 @@
         <v>0.0717</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2514416243843697</v>
+        <v>0.2496077663963303</v>
       </c>
       <c r="J4" t="n">
+        <v>469</v>
+      </c>
+      <c r="K4" t="n">
         <v>468</v>
       </c>
-      <c r="K4" t="n">
-        <v>467</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.08891613776307317</v>
+        <v>0.08802256718897628</v>
       </c>
       <c r="M4" t="n">
-        <v>4.433348870942426</v>
+        <v>4.43100633079732</v>
       </c>
       <c r="N4" t="n">
-        <v>35.89760308342955</v>
+        <v>35.86079034304307</v>
       </c>
       <c r="O4" t="n">
-        <v>5.991460847191572</v>
+        <v>5.988387958628188</v>
       </c>
       <c r="P4" t="n">
-        <v>237.4786289842496</v>
+        <v>237.4979951372523</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22755,28 +22801,28 @@
         <v>0.141</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1455874876044856</v>
+        <v>0.1422896574799575</v>
       </c>
       <c r="J5" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K5" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08109628156795046</v>
+        <v>0.07738560689213025</v>
       </c>
       <c r="M5" t="n">
-        <v>2.904731225220434</v>
+        <v>2.913081726214625</v>
       </c>
       <c r="N5" t="n">
-        <v>13.40454183711812</v>
+        <v>13.50632241963448</v>
       </c>
       <c r="O5" t="n">
-        <v>3.661221358661358</v>
+        <v>3.675094885800158</v>
       </c>
       <c r="P5" t="n">
-        <v>218.7562635779196</v>
+        <v>218.7909106354301</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22827,28 +22873,28 @@
         <v>0.0611</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4252707742062529</v>
+        <v>-0.4264476284160777</v>
       </c>
       <c r="J6" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K6" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L6" t="n">
-        <v>0.364580708942997</v>
+        <v>0.3667236878324748</v>
       </c>
       <c r="M6" t="n">
-        <v>3.167738890477199</v>
+        <v>3.166128099539044</v>
       </c>
       <c r="N6" t="n">
-        <v>17.59270377581113</v>
+        <v>17.57179385306154</v>
       </c>
       <c r="O6" t="n">
-        <v>4.194365717937711</v>
+        <v>4.191872356484812</v>
       </c>
       <c r="P6" t="n">
-        <v>219.7970373479465</v>
+        <v>219.8094013976245</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22899,28 +22945,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.005531046808272305</v>
+        <v>0.009368343084225319</v>
       </c>
       <c r="J7" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K7" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L7" t="n">
-        <v>9.709806339752713e-05</v>
+        <v>0.0002770250098778071</v>
       </c>
       <c r="M7" t="n">
-        <v>3.193294617741275</v>
+        <v>3.20638669067443</v>
       </c>
       <c r="N7" t="n">
-        <v>17.5831520777385</v>
+        <v>17.72216110136169</v>
       </c>
       <c r="O7" t="n">
-        <v>4.193226928957995</v>
+        <v>4.209769720704648</v>
       </c>
       <c r="P7" t="n">
-        <v>225.8752786435809</v>
+        <v>225.8349639458138</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22971,28 +23017,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00195046553254177</v>
+        <v>0.001915019517973813</v>
       </c>
       <c r="J8" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K8" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L8" t="n">
-        <v>8.639537531496266e-06</v>
+        <v>8.367250948104754e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>3.046460510686613</v>
+        <v>3.040067945644179</v>
       </c>
       <c r="N8" t="n">
-        <v>24.5763348978833</v>
+        <v>24.52394839105089</v>
       </c>
       <c r="O8" t="n">
-        <v>4.957452460476379</v>
+        <v>4.952166030238778</v>
       </c>
       <c r="P8" t="n">
-        <v>213.869571273107</v>
+        <v>213.8699436695188</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23043,28 +23089,28 @@
         <v>0.1106</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1162691588262145</v>
+        <v>-0.1153389888263549</v>
       </c>
       <c r="J9" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K9" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04245095225522721</v>
+        <v>0.04196511499315636</v>
       </c>
       <c r="M9" t="n">
-        <v>2.949526985334749</v>
+        <v>2.947888162369345</v>
       </c>
       <c r="N9" t="n">
-        <v>17.01913396789699</v>
+        <v>16.99321677511714</v>
       </c>
       <c r="O9" t="n">
-        <v>4.125425307516426</v>
+        <v>4.122282956702165</v>
       </c>
       <c r="P9" t="n">
-        <v>202.0765971310792</v>
+        <v>202.0668247497671</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23102,7 +23148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J469"/>
+  <dimension ref="A1:J470"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47477,6 +47523,58 @@
         </is>
       </c>
     </row>
+    <row r="470">
+      <c r="A470" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:27:30+00:00</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>-46.89704178815805,168.13078808188834</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>-46.89783422645157,168.12907420748576</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>-46.89853576388222,168.12951484172467</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>-46.898982847740974,168.12985953681837</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>-46.899556507640455,168.13050246973856</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>-46.899889446903465,168.13150904090318</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>-46.90018972804063,168.13221176439603</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>-46.900468749955806,168.13319212457796</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0589/nzd0589.xlsx
+++ b/data/nzd0589/nzd0589.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J470"/>
+  <dimension ref="A1:J471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17345,7 +17345,7 @@
         <v>205.68</v>
       </c>
       <c r="G470" t="n">
-        <v>235.15</v>
+        <v>228.18</v>
       </c>
       <c r="H470" t="n">
         <v>213.84</v>
@@ -17356,6 +17356,42 @@
       <c r="J470" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:27:18+00:00</t>
+        </is>
+      </c>
+      <c r="B471" t="n">
+        <v>346.77</v>
+      </c>
+      <c r="C471" t="n">
+        <v>210.87</v>
+      </c>
+      <c r="D471" t="n">
+        <v>238.69</v>
+      </c>
+      <c r="E471" t="n">
+        <v>215.34</v>
+      </c>
+      <c r="F471" t="n">
+        <v>204.98</v>
+      </c>
+      <c r="G471" t="n">
+        <v>225.03</v>
+      </c>
+      <c r="H471" t="n">
+        <v>213.11</v>
+      </c>
+      <c r="I471" t="n">
+        <v>201.44</v>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -17370,7 +17406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B505"/>
+  <dimension ref="A1:B506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22423,6 +22459,16 @@
       </c>
       <c r="B505" t="n">
         <v>-0.25</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -22585,28 +22631,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1078943882607164</v>
+        <v>0.112152997060008</v>
       </c>
       <c r="J2" t="n">
+        <v>470</v>
+      </c>
+      <c r="K2" t="n">
         <v>469</v>
       </c>
-      <c r="K2" t="n">
-        <v>468</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.001223859797066296</v>
+        <v>0.001327827753521471</v>
       </c>
       <c r="M2" t="n">
-        <v>15.79615583140257</v>
+        <v>15.77473637475995</v>
       </c>
       <c r="N2" t="n">
-        <v>532.3072196735257</v>
+        <v>531.3917607966732</v>
       </c>
       <c r="O2" t="n">
-        <v>23.07178405918202</v>
+        <v>23.05193616156077</v>
       </c>
       <c r="P2" t="n">
-        <v>333.7192576250069</v>
+        <v>333.6744815677642</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22657,28 +22703,28 @@
         <v>0.1473</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0860035828920071</v>
+        <v>0.0846039564548767</v>
       </c>
       <c r="J3" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K3" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03543444475561075</v>
+        <v>0.03441338403791039</v>
       </c>
       <c r="M3" t="n">
-        <v>2.641721261881967</v>
+        <v>2.641807527291549</v>
       </c>
       <c r="N3" t="n">
-        <v>11.29252622826453</v>
+        <v>11.29215533694676</v>
       </c>
       <c r="O3" t="n">
-        <v>3.360435422421405</v>
+        <v>3.360380236959317</v>
       </c>
       <c r="P3" t="n">
-        <v>211.9254378388652</v>
+        <v>211.9401558415467</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22729,28 +22775,28 @@
         <v>0.0717</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2496077663963303</v>
+        <v>0.2473123462108533</v>
       </c>
       <c r="J4" t="n">
+        <v>470</v>
+      </c>
+      <c r="K4" t="n">
         <v>469</v>
       </c>
-      <c r="K4" t="n">
-        <v>468</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.08802256718897628</v>
+        <v>0.08677941301124192</v>
       </c>
       <c r="M4" t="n">
-        <v>4.43100633079732</v>
+        <v>4.430444947289639</v>
       </c>
       <c r="N4" t="n">
-        <v>35.86079034304307</v>
+        <v>35.8472965518806</v>
       </c>
       <c r="O4" t="n">
-        <v>5.988387958628188</v>
+        <v>5.987261189549075</v>
       </c>
       <c r="P4" t="n">
-        <v>237.4979951372523</v>
+        <v>237.5222585899339</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22801,28 +22847,28 @@
         <v>0.141</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1422896574799575</v>
+        <v>0.1392590113357735</v>
       </c>
       <c r="J5" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K5" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07738560689213025</v>
+        <v>0.07412194189228638</v>
       </c>
       <c r="M5" t="n">
-        <v>2.913081726214625</v>
+        <v>2.920386260157358</v>
       </c>
       <c r="N5" t="n">
-        <v>13.50632241963448</v>
+        <v>13.58850383753536</v>
       </c>
       <c r="O5" t="n">
-        <v>3.675094885800158</v>
+        <v>3.686258786023488</v>
       </c>
       <c r="P5" t="n">
-        <v>218.7909106354301</v>
+        <v>218.8227811194972</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22873,28 +22919,28 @@
         <v>0.0611</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4264476284160777</v>
+        <v>-0.4278998639633235</v>
       </c>
       <c r="J6" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K6" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3667236878324748</v>
+        <v>0.3690449685971651</v>
       </c>
       <c r="M6" t="n">
-        <v>3.166128099539044</v>
+        <v>3.165725510081546</v>
       </c>
       <c r="N6" t="n">
-        <v>17.57179385306154</v>
+        <v>17.55987575696678</v>
       </c>
       <c r="O6" t="n">
-        <v>4.191872356484812</v>
+        <v>4.190450543434056</v>
       </c>
       <c r="P6" t="n">
-        <v>219.8094013976245</v>
+        <v>219.8246732068917</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22945,28 +22991,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009368343084225319</v>
+        <v>0.006020174253784514</v>
       </c>
       <c r="J7" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K7" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002770250098778071</v>
+        <v>0.0001160228202238267</v>
       </c>
       <c r="M7" t="n">
-        <v>3.20638669067443</v>
+        <v>3.186480569022437</v>
       </c>
       <c r="N7" t="n">
-        <v>17.72216110136169</v>
+        <v>17.52033226412752</v>
       </c>
       <c r="O7" t="n">
-        <v>4.209769720704648</v>
+        <v>4.185729597588397</v>
       </c>
       <c r="P7" t="n">
-        <v>225.8349639458138</v>
+        <v>225.8701440802441</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23017,28 +23063,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001915019517973813</v>
+        <v>0.001573987435333096</v>
       </c>
       <c r="J8" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K8" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L8" t="n">
-        <v>8.367250948104754e-06</v>
+        <v>5.678423457777804e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>3.040067945644179</v>
+        <v>3.034586616088711</v>
       </c>
       <c r="N8" t="n">
-        <v>24.52394839105089</v>
+        <v>24.47317428188787</v>
       </c>
       <c r="O8" t="n">
-        <v>4.952166030238778</v>
+        <v>4.947036919398103</v>
       </c>
       <c r="P8" t="n">
-        <v>213.8699436695188</v>
+        <v>213.8735299864424</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23089,28 +23135,28 @@
         <v>0.1106</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1153389888263549</v>
+        <v>-0.1143150775204269</v>
       </c>
       <c r="J9" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K9" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04196511499315636</v>
+        <v>0.04140798895407449</v>
       </c>
       <c r="M9" t="n">
-        <v>2.947888162369345</v>
+        <v>2.946715473881829</v>
       </c>
       <c r="N9" t="n">
-        <v>16.99321677511714</v>
+        <v>16.96972168306089</v>
       </c>
       <c r="O9" t="n">
-        <v>4.122282956702165</v>
+        <v>4.119432203964631</v>
       </c>
       <c r="P9" t="n">
-        <v>202.0668247497671</v>
+        <v>202.0560572277901</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23148,7 +23194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J470"/>
+  <dimension ref="A1:J471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47556,7 +47602,7 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>-46.899889446903465,168.13150904090318</t>
+          <t>-46.89993293466364,168.13144331278036</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -47572,6 +47618,58 @@
       <c r="J470" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:27:18+00:00</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>-46.89704192076637,168.13078494237905</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>-46.89783433691765,168.12907159118876</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>-46.898536391227594,168.12949992842488</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>-46.898979350765416,168.12986481339718</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>-46.899560875787266,168.13049586960736</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>-46.899952588372166,168.1314136077832</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>-46.9001961026505,168.13220951675967</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>-46.90046665418607,168.13319286349366</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0589/nzd0589.xlsx
+++ b/data/nzd0589/nzd0589.xlsx
@@ -17345,7 +17345,7 @@
         <v>205.68</v>
       </c>
       <c r="G470" t="n">
-        <v>228.18</v>
+        <v>235.15</v>
       </c>
       <c r="H470" t="n">
         <v>213.84</v>
@@ -17381,7 +17381,7 @@
         <v>204.98</v>
       </c>
       <c r="G471" t="n">
-        <v>225.03</v>
+        <v>231.48</v>
       </c>
       <c r="H471" t="n">
         <v>213.11</v>
@@ -17406,7 +17406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B506"/>
+  <dimension ref="A1:B507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22469,6 +22469,16 @@
       </c>
       <c r="B506" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>0.64</v>
       </c>
     </row>
   </sheetData>
@@ -22991,7 +23001,7 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.006020174253784514</v>
+        <v>0.01162405183350447</v>
       </c>
       <c r="J7" t="n">
         <v>470</v>
@@ -23000,19 +23010,19 @@
         <v>470</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001160228202238267</v>
+        <v>0.0004269230387555778</v>
       </c>
       <c r="M7" t="n">
-        <v>3.186480569022437</v>
+        <v>3.211216246679647</v>
       </c>
       <c r="N7" t="n">
-        <v>17.52033226412752</v>
+        <v>17.74590109323279</v>
       </c>
       <c r="O7" t="n">
-        <v>4.185729597588397</v>
+        <v>4.212588407764613</v>
       </c>
       <c r="P7" t="n">
-        <v>225.8701440802441</v>
+        <v>225.8112427568878</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -47602,7 +47612,7 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>-46.89993293466364,168.13144331278036</t>
+          <t>-46.899889446903465,168.13150904090318</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -47654,7 +47664,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>-46.899952588372166,168.1314136077832</t>
+          <t>-46.899912345055014,168.13147443227788</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">

--- a/data/nzd0589/nzd0589.xlsx
+++ b/data/nzd0589/nzd0589.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J471"/>
+  <dimension ref="A1:J474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17390,6 +17390,114 @@
         <v>201.44</v>
       </c>
       <c r="J471" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:41+00:00</t>
+        </is>
+      </c>
+      <c r="B472" t="n">
+        <v>347.43</v>
+      </c>
+      <c r="C472" t="n">
+        <v>213.49</v>
+      </c>
+      <c r="D472" t="n">
+        <v>244.21</v>
+      </c>
+      <c r="E472" t="n">
+        <v>217.33</v>
+      </c>
+      <c r="F472" t="n">
+        <v>206.79</v>
+      </c>
+      <c r="G472" t="n">
+        <v>230.93</v>
+      </c>
+      <c r="H472" t="n">
+        <v>213.82</v>
+      </c>
+      <c r="I472" t="n">
+        <v>201.24</v>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:26:49+00:00</t>
+        </is>
+      </c>
+      <c r="B473" t="n">
+        <v>326.79</v>
+      </c>
+      <c r="C473" t="n">
+        <v>216.26</v>
+      </c>
+      <c r="D473" t="n">
+        <v>246.42</v>
+      </c>
+      <c r="E473" t="n">
+        <v>219.72</v>
+      </c>
+      <c r="F473" t="n">
+        <v>207.91</v>
+      </c>
+      <c r="G473" t="n">
+        <v>229.22</v>
+      </c>
+      <c r="H473" t="n">
+        <v>213.89</v>
+      </c>
+      <c r="I473" t="n">
+        <v>202.16</v>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B474" t="n">
+        <v>312.39</v>
+      </c>
+      <c r="C474" t="n">
+        <v>215.94</v>
+      </c>
+      <c r="D474" t="n">
+        <v>247.08</v>
+      </c>
+      <c r="E474" t="n">
+        <v>219.75</v>
+      </c>
+      <c r="F474" t="n">
+        <v>208.68</v>
+      </c>
+      <c r="G474" t="n">
+        <v>229.78</v>
+      </c>
+      <c r="H474" t="n">
+        <v>214.09</v>
+      </c>
+      <c r="I474" t="n">
+        <v>202.58</v>
+      </c>
+      <c r="J474" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -17406,7 +17514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B507"/>
+  <dimension ref="A1:B510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22479,6 +22587,36 @@
       </c>
       <c r="B507" t="n">
         <v>0.64</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>0.26</v>
       </c>
     </row>
   </sheetData>
@@ -22641,28 +22779,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.112152997060008</v>
+        <v>0.1023575094455852</v>
       </c>
       <c r="J2" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K2" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001327827753521471</v>
+        <v>0.001118365089262885</v>
       </c>
       <c r="M2" t="n">
-        <v>15.77473637475995</v>
+        <v>15.79086702295621</v>
       </c>
       <c r="N2" t="n">
-        <v>531.3917607966732</v>
+        <v>529.7092743887198</v>
       </c>
       <c r="O2" t="n">
-        <v>23.05193616156077</v>
+        <v>23.01541384352495</v>
       </c>
       <c r="P2" t="n">
-        <v>333.6744815677642</v>
+        <v>333.7784490121315</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22713,28 +22851,28 @@
         <v>0.1473</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0846039564548767</v>
+        <v>0.08588008777863655</v>
       </c>
       <c r="J3" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K3" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03441338403791039</v>
+        <v>0.03585707836219509</v>
       </c>
       <c r="M3" t="n">
-        <v>2.641807527291549</v>
+        <v>2.6357450393097</v>
       </c>
       <c r="N3" t="n">
-        <v>11.29215533694676</v>
+        <v>11.23640211718143</v>
       </c>
       <c r="O3" t="n">
-        <v>3.360380236959317</v>
+        <v>3.3520743006654</v>
       </c>
       <c r="P3" t="n">
-        <v>211.9401558415467</v>
+        <v>211.9266151305194</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22785,28 +22923,28 @@
         <v>0.0717</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2473123462108533</v>
+        <v>0.2495137931237847</v>
       </c>
       <c r="J4" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K4" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08677941301124192</v>
+        <v>0.08927503779369783</v>
       </c>
       <c r="M4" t="n">
-        <v>4.430444947289639</v>
+        <v>4.415750890206224</v>
       </c>
       <c r="N4" t="n">
-        <v>35.8472965518806</v>
+        <v>35.64792109212847</v>
       </c>
       <c r="O4" t="n">
-        <v>5.987261189549075</v>
+        <v>5.970588002209537</v>
       </c>
       <c r="P4" t="n">
-        <v>237.5222585899339</v>
+        <v>237.4987908264758</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22857,28 +22995,28 @@
         <v>0.141</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1392590113357735</v>
+        <v>0.1347354850227125</v>
       </c>
       <c r="J5" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K5" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07412194189228638</v>
+        <v>0.07020338732151177</v>
       </c>
       <c r="M5" t="n">
-        <v>2.920386260157358</v>
+        <v>2.921639880514014</v>
       </c>
       <c r="N5" t="n">
-        <v>13.58850383753536</v>
+        <v>13.59187793066635</v>
       </c>
       <c r="O5" t="n">
-        <v>3.686258786023488</v>
+        <v>3.686716415818601</v>
       </c>
       <c r="P5" t="n">
-        <v>218.8227811194972</v>
+        <v>218.8707161997694</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22929,28 +23067,28 @@
         <v>0.0611</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4278998639633235</v>
+        <v>-0.4285961771747077</v>
       </c>
       <c r="J6" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K6" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3690449685971651</v>
+        <v>0.3730200551025007</v>
       </c>
       <c r="M6" t="n">
-        <v>3.165725510081546</v>
+        <v>3.15010304078984</v>
       </c>
       <c r="N6" t="n">
-        <v>17.55987575696678</v>
+        <v>17.4543486444409</v>
       </c>
       <c r="O6" t="n">
-        <v>4.190450543434056</v>
+        <v>4.177840188954204</v>
       </c>
       <c r="P6" t="n">
-        <v>219.8246732068917</v>
+        <v>219.8320455088504</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23001,28 +23139,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01162405183350447</v>
+        <v>0.0164379932176144</v>
       </c>
       <c r="J7" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K7" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004269230387555778</v>
+        <v>0.0008608562649953244</v>
       </c>
       <c r="M7" t="n">
-        <v>3.211216246679647</v>
+        <v>3.215178248632018</v>
       </c>
       <c r="N7" t="n">
-        <v>17.74590109323279</v>
+        <v>17.72876634331292</v>
       </c>
       <c r="O7" t="n">
-        <v>4.212588407764613</v>
+        <v>4.210554161071072</v>
       </c>
       <c r="P7" t="n">
-        <v>225.8112427568878</v>
+        <v>225.7602240165511</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23073,28 +23211,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001573987435333096</v>
+        <v>0.001596080304544164</v>
       </c>
       <c r="J8" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K8" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L8" t="n">
-        <v>5.678423457777804e-06</v>
+        <v>5.921938888375777e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>3.034586616088711</v>
+        <v>3.016019808042532</v>
       </c>
       <c r="N8" t="n">
-        <v>24.47317428188787</v>
+        <v>24.31804046298507</v>
       </c>
       <c r="O8" t="n">
-        <v>4.947036919398103</v>
+        <v>4.931332524073495</v>
       </c>
       <c r="P8" t="n">
-        <v>213.8735299864424</v>
+        <v>213.8732948186604</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23145,28 +23283,28 @@
         <v>0.1106</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1143150775204269</v>
+        <v>-0.1105592317728284</v>
       </c>
       <c r="J9" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K9" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04140798895407449</v>
+        <v>0.03923632797629117</v>
       </c>
       <c r="M9" t="n">
-        <v>2.946715473881829</v>
+        <v>2.946403142608541</v>
       </c>
       <c r="N9" t="n">
-        <v>16.96972168306089</v>
+        <v>16.92013543069039</v>
       </c>
       <c r="O9" t="n">
-        <v>4.119432203964631</v>
+        <v>4.113409222371438</v>
       </c>
       <c r="P9" t="n">
-        <v>202.0560572277901</v>
+        <v>202.0162402508721</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23204,7 +23342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J471"/>
+  <dimension ref="A1:J474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47683,6 +47821,162 @@
         </is>
       </c>
     </row>
+    <row r="472">
+      <c r="A472" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:41+00:00</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>-46.897041556093235,168.1307935760296</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>-46.8978328898073,168.1291058646786</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>-46.89853335353698,168.1295721401905</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>-46.89896692401079,168.1298835640914</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>-46.89954958100677,168.13051293565871</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>-46.89991577665711,168.13146924569662</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>-46.90018990268748,168.13221170281696</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>-46.900468400660834,168.1331922477306</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:26:49+00:00</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>-46.897052960105334,168.13052357819973</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>-46.89783135983588,168.12914210039</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>-46.89853213734724,168.12960105105913</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>-46.89895199941154,168.1299060837579</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>-46.89954259196991,168.13052349586368</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>-46.8999264458183,168.13145312013975</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>-46.90018929142351,168.1322119183437</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>-46.900460366876835,168.13319508024037</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>-46.89706091601193,168.13033520758256</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>-46.897831536584064,168.1291379143151</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>-46.89853177413982,168.12960968507406</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>-46.89895181207345,168.12990636643147</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>-46.899537787006444,168.13053075600303</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>-46.899922951824266,168.1314584010246</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>-46.90018754495504,168.1322125341344</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>-46.90045669927975,168.13319637334234</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0589/nzd0589.xlsx
+++ b/data/nzd0589/nzd0589.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J474"/>
+  <dimension ref="A1:J479"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17438,7 +17438,7 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>326.79</v>
+        <v>347.13</v>
       </c>
       <c r="C473" t="n">
         <v>216.26</v>
@@ -17474,7 +17474,7 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>312.39</v>
+        <v>347.13</v>
       </c>
       <c r="C474" t="n">
         <v>215.94</v>
@@ -17500,6 +17500,186 @@
       <c r="J474" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-30 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B475" t="n">
+        <v>344.77</v>
+      </c>
+      <c r="C475" t="n">
+        <v>217.03</v>
+      </c>
+      <c r="D475" t="n">
+        <v>245.68</v>
+      </c>
+      <c r="E475" t="n">
+        <v>219.04</v>
+      </c>
+      <c r="F475" t="n">
+        <v>206.71</v>
+      </c>
+      <c r="G475" t="n">
+        <v>224.65</v>
+      </c>
+      <c r="H475" t="n">
+        <v>211.39</v>
+      </c>
+      <c r="I475" t="n">
+        <v>199.88</v>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-07 22:26:27+00:00</t>
+        </is>
+      </c>
+      <c r="B476" t="n">
+        <v>346.6</v>
+      </c>
+      <c r="C476" t="n">
+        <v>216.45</v>
+      </c>
+      <c r="D476" t="n">
+        <v>244.98</v>
+      </c>
+      <c r="E476" t="n">
+        <v>219.1</v>
+      </c>
+      <c r="F476" t="n">
+        <v>203.4</v>
+      </c>
+      <c r="G476" t="n">
+        <v>224.03</v>
+      </c>
+      <c r="H476" t="n">
+        <v>209.4</v>
+      </c>
+      <c r="I476" t="n">
+        <v>197.81</v>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:27+00:00</t>
+        </is>
+      </c>
+      <c r="B477" t="n">
+        <v>346.6</v>
+      </c>
+      <c r="C477" t="n">
+        <v>214.95</v>
+      </c>
+      <c r="D477" t="n">
+        <v>243.42</v>
+      </c>
+      <c r="E477" t="n">
+        <v>218.02</v>
+      </c>
+      <c r="F477" t="n">
+        <v>203.35</v>
+      </c>
+      <c r="G477" t="n">
+        <v>222.31</v>
+      </c>
+      <c r="H477" t="n">
+        <v>208.98</v>
+      </c>
+      <c r="I477" t="n">
+        <v>197.32</v>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:23+00:00</t>
+        </is>
+      </c>
+      <c r="B478" t="n">
+        <v>345.47</v>
+      </c>
+      <c r="C478" t="n">
+        <v>213</v>
+      </c>
+      <c r="D478" t="n">
+        <v>239.75</v>
+      </c>
+      <c r="E478" t="n">
+        <v>216.25</v>
+      </c>
+      <c r="F478" t="n">
+        <v>201.93</v>
+      </c>
+      <c r="G478" t="n">
+        <v>221.41</v>
+      </c>
+      <c r="H478" t="n">
+        <v>207.35</v>
+      </c>
+      <c r="I478" t="n">
+        <v>195.79</v>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:38+00:00</t>
+        </is>
+      </c>
+      <c r="B479" t="n">
+        <v>333.49</v>
+      </c>
+      <c r="C479" t="n">
+        <v>212.5</v>
+      </c>
+      <c r="D479" t="n">
+        <v>240.14</v>
+      </c>
+      <c r="E479" t="n">
+        <v>216.09</v>
+      </c>
+      <c r="F479" t="n">
+        <v>202.94</v>
+      </c>
+      <c r="G479" t="n">
+        <v>221.41</v>
+      </c>
+      <c r="H479" t="n">
+        <v>208.22</v>
+      </c>
+      <c r="I479" t="n">
+        <v>196.62</v>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -17514,7 +17694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B510"/>
+  <dimension ref="A1:B515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22617,6 +22797,56 @@
       </c>
       <c r="B510" t="n">
         <v>0.26</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-05-30 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-06-07 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>0.68</v>
       </c>
     </row>
   </sheetData>
@@ -22779,28 +23009,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1023575094455852</v>
+        <v>0.1384833802092909</v>
       </c>
       <c r="J2" t="n">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="K2" t="n">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001118365089262885</v>
+        <v>0.002094001539445278</v>
       </c>
       <c r="M2" t="n">
-        <v>15.79086702295621</v>
+        <v>15.60291647500164</v>
       </c>
       <c r="N2" t="n">
-        <v>529.7092743887198</v>
+        <v>523.8531937526044</v>
       </c>
       <c r="O2" t="n">
-        <v>23.01541384352495</v>
+        <v>22.88783942954434</v>
       </c>
       <c r="P2" t="n">
-        <v>333.7784490121315</v>
+        <v>333.3949826716623</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22851,28 +23081,28 @@
         <v>0.1473</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08588008777863655</v>
+        <v>0.08698670846392632</v>
       </c>
       <c r="J3" t="n">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="K3" t="n">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03585707836219509</v>
+        <v>0.0374561765387571</v>
       </c>
       <c r="M3" t="n">
-        <v>2.6357450393097</v>
+        <v>2.627360844616057</v>
       </c>
       <c r="N3" t="n">
-        <v>11.23640211718143</v>
+        <v>11.15561113979986</v>
       </c>
       <c r="O3" t="n">
-        <v>3.3520743006654</v>
+        <v>3.340001667634294</v>
       </c>
       <c r="P3" t="n">
-        <v>211.9266151305194</v>
+        <v>211.9148782140603</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22923,28 +23153,28 @@
         <v>0.0717</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2495137931237847</v>
+        <v>0.246604672510324</v>
       </c>
       <c r="J4" t="n">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="K4" t="n">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08927503779369783</v>
+        <v>0.08905886151563736</v>
       </c>
       <c r="M4" t="n">
-        <v>4.415750890206224</v>
+        <v>4.390610965478223</v>
       </c>
       <c r="N4" t="n">
-        <v>35.64792109212847</v>
+        <v>35.35736699449625</v>
       </c>
       <c r="O4" t="n">
-        <v>5.970588002209537</v>
+        <v>5.946206100909743</v>
       </c>
       <c r="P4" t="n">
-        <v>237.4987908264758</v>
+        <v>237.5299502891237</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22995,28 +23225,28 @@
         <v>0.141</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1347354850227125</v>
+        <v>0.1249905744985465</v>
       </c>
       <c r="J5" t="n">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="K5" t="n">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07020338732151177</v>
+        <v>0.06127720850539597</v>
       </c>
       <c r="M5" t="n">
-        <v>2.921639880514014</v>
+        <v>2.933973402988374</v>
       </c>
       <c r="N5" t="n">
-        <v>13.59187793066635</v>
+        <v>13.700347769687</v>
       </c>
       <c r="O5" t="n">
-        <v>3.686716415818601</v>
+        <v>3.701398083114946</v>
       </c>
       <c r="P5" t="n">
-        <v>218.8707161997694</v>
+        <v>218.9744267494959</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23067,28 +23297,28 @@
         <v>0.0611</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4285961771747077</v>
+        <v>-0.4380164235011276</v>
       </c>
       <c r="J6" t="n">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="K6" t="n">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3730200551025007</v>
+        <v>0.3853796710352686</v>
       </c>
       <c r="M6" t="n">
-        <v>3.15010304078984</v>
+        <v>3.157908872820539</v>
       </c>
       <c r="N6" t="n">
-        <v>17.4543486444409</v>
+        <v>17.51610669412642</v>
       </c>
       <c r="O6" t="n">
-        <v>4.177840188954204</v>
+        <v>4.185224808075</v>
       </c>
       <c r="P6" t="n">
-        <v>219.8320455088504</v>
+        <v>219.9323023346134</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23139,28 +23369,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0164379932176144</v>
+        <v>0.009443013204845054</v>
       </c>
       <c r="J7" t="n">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="K7" t="n">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0008608562649953244</v>
+        <v>0.0002886032438450536</v>
       </c>
       <c r="M7" t="n">
-        <v>3.215178248632018</v>
+        <v>3.216496230012884</v>
       </c>
       <c r="N7" t="n">
-        <v>17.72876634331292</v>
+        <v>17.68207801020116</v>
       </c>
       <c r="O7" t="n">
-        <v>4.210554161071072</v>
+        <v>4.205006303229658</v>
       </c>
       <c r="P7" t="n">
-        <v>225.7602240165511</v>
+        <v>225.834675641503</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23211,28 +23441,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001596080304544164</v>
+        <v>-0.00825458353340401</v>
       </c>
       <c r="J8" t="n">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="K8" t="n">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="L8" t="n">
-        <v>5.921938888375777e-06</v>
+        <v>0.0001603556885508839</v>
       </c>
       <c r="M8" t="n">
-        <v>3.016019808042532</v>
+        <v>3.014133761817564</v>
       </c>
       <c r="N8" t="n">
-        <v>24.31804046298507</v>
+        <v>24.32063941457496</v>
       </c>
       <c r="O8" t="n">
-        <v>4.931332524073495</v>
+        <v>4.93159603116222</v>
       </c>
       <c r="P8" t="n">
-        <v>213.8732948186604</v>
+        <v>213.9781293474637</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23283,28 +23513,28 @@
         <v>0.1106</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1105592317728284</v>
+        <v>-0.113733800475109</v>
       </c>
       <c r="J9" t="n">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="K9" t="n">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03923632797629117</v>
+        <v>0.04224584605305226</v>
       </c>
       <c r="M9" t="n">
-        <v>2.946403142608541</v>
+        <v>2.935594491670662</v>
       </c>
       <c r="N9" t="n">
-        <v>16.92013543069039</v>
+        <v>16.78756892015065</v>
       </c>
       <c r="O9" t="n">
-        <v>4.113409222371438</v>
+        <v>4.097263589293548</v>
       </c>
       <c r="P9" t="n">
-        <v>202.0162402508721</v>
+        <v>202.0500424743647</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23342,7 +23572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J474"/>
+  <dimension ref="A1:J479"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47881,7 +48111,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>-46.897052960105334,168.13052357819973</t>
+          <t>-46.897041721853846,168.130789651643</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -47933,7 +48163,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>-46.89706091601193,168.13033520758256</t>
+          <t>-46.897041721853846,168.130789651643</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -47974,6 +48204,266 @@
       <c r="J474" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-30 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>-46.89704302583245,168.13075877980125</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>-46.8978309345349,168.1291521731327</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>-46.89853254457902,168.12959137049685</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>-46.89895624574154,168.12989967649006</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>-46.89955008022365,168.13051218135826</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>-46.89995495929516,168.13141002432172</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>-46.90021112227896,168.13220422095654</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>-46.90048027668918,168.13318806054048</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-07 22:26:27+00:00</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>-46.89704201469722,168.13078271855997</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>-46.89783125489156,168.12914458587196</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>-46.898532929797504,168.12958221320815</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>-46.89895587106538,168.12990024183725</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>-46.899570735317084,168.13048097216438</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>-46.89995882764292,168.1314041776208</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>-46.90022849963932,168.1321980938314</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>-46.90049835270244,168.13318168738687</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:27+00:00</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>-46.89704201469722,168.13078271855997</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>-46.897832083397816,168.12912496364578</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>-46.89853378828176,168.1295618055359</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>-46.89896261523579,168.12989006558638</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>-46.899571047327484,168.13048050072624</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>-46.89996955918657,168.1313879577364</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>-46.90023216722286,168.1321968006687</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>-46.900502631565395,168.1331801787653</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:23+00:00</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>-46.89704263906002,168.13076793670356</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>-46.897833160450865,168.1290994547512</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>-46.89853580790651,168.12951379517733</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>-46.89897366817954,168.12987338783634</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>-46.89957990842201,168.13046711188028</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>-46.89997517452817,168.131379470585</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>-46.90024640093968,168.13219178196422</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>-46.90051599209647,168.1331754681696</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:38+00:00</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>-46.89704925829206,168.13061122285117</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>-46.89783343661738,168.1290929140089</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>-46.89853559328795,168.12951889709566</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>-46.898974667315585,168.12987188024275</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>-46.899573605812705,168.13047663493313</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>-46.89997517452817,168.131379470585</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>-46.90023880380252,168.13219446065963</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>-46.900508744226705,168.13317802359114</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
